--- a/InputData/io-model/PoNDHbE/Perc of National Debt Held by Entity.xlsx
+++ b/InputData/io-model/PoNDHbE/Perc of National Debt Held by Entity.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10420"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sarrynna\Dropbox (CEA)\Energy Innovation IO\Deliverable IO files\Mexico\PoNDHbE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andreazafra/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD763A9C-DEB4-4926-99FD-323A9FBF1FEF}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A8947A7-4F80-E84C-BECF-0F476D27C230}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{451D0B24-AF55-4E31-8A85-DA035DBAD1DC}"/>
+    <workbookView xWindow="32580" yWindow="1340" windowWidth="31380" windowHeight="18520" activeTab="2" xr2:uid="{451D0B24-AF55-4E31-8A85-DA035DBAD1DC}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -34,8 +34,26 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={767A6EB5-AA15-9841-8FFA-C6DE2D457FE8}</author>
+  </authors>
+  <commentList>
+    <comment ref="C14" authorId="0" shapeId="0" xr:uid="{767A6EB5-AA15-9841-8FFA-C6DE2D457FE8}">
+      <text>
+        <t>[Comentario encadenado]
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
+    Is it constant?</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="83">
   <si>
     <t>PoNDHbE Percent of National Debt Held by Entity</t>
   </si>
@@ -215,9 +233,6 @@
     <t>see variable io-model/PoNDHbE for the US</t>
   </si>
   <si>
-    <t>Peso: Dollar Exchange (2019, average closing price)</t>
-  </si>
-  <si>
     <t>https://www.macrotrends.net/2559/us-dollar-mexican-peso-exchange-rate-historical-chart</t>
   </si>
   <si>
@@ -254,15 +269,6 @@
     <t xml:space="preserve">https://fred.stlouisfed.org/series/GGGDTAMXA188N </t>
   </si>
   <si>
-    <t>billion U.S. dollars</t>
-  </si>
-  <si>
-    <t>MEX per-capita GDP (2019)</t>
-  </si>
-  <si>
-    <t>U.S. per-capita GDP (2019)</t>
-  </si>
-  <si>
     <t>Total Mex Foreign Debt (b USD)</t>
   </si>
   <si>
@@ -279,17 +285,48 @@
   </si>
   <si>
     <t>is multiplied by the IDN:US GDP per capita ratio, under the assumption that</t>
+  </si>
+  <si>
+    <t>MEX per-capita GDP (2023)</t>
+  </si>
+  <si>
+    <t>U.S. per-capita GDP (2023)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">External debt stocks, total. </t>
+  </si>
+  <si>
+    <t>World Bank, 2023</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>Variable</t>
+  </si>
+  <si>
+    <t>billion U.S. dollars, 2023</t>
+  </si>
+  <si>
+    <t>Peso: Dollar Exchange (2023, average closing price)</t>
+  </si>
+  <si>
+    <t>=</t>
+  </si>
+  <si>
+    <t>FRED Economic data (% of GDP)*Mexican PIB</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="170" formatCode="0.000E+00"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -332,6 +369,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -447,11 +490,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -463,12 +506,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="4" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -477,45 +517,41 @@
     <xf numFmtId="9" fontId="0" fillId="3" borderId="3" xfId="4" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="3" borderId="5" xfId="4" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="3" borderId="8" xfId="4" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="5" applyFont="1" applyFill="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="5" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="3" borderId="3" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="3" borderId="5" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="3" borderId="8" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="2" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="2" borderId="0" xfId="4" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="6">
-    <cellStyle name="Comma" xfId="5" builtinId="3"/>
-    <cellStyle name="Currency" xfId="3" builtinId="4"/>
-    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
+    <cellStyle name="Millares" xfId="5" builtinId="3"/>
+    <cellStyle name="Moneda" xfId="3" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{00B5581E-B353-45CF-825C-BCADC57BBDF5}"/>
-    <cellStyle name="Percent" xfId="4" builtinId="5"/>
+    <cellStyle name="Porcentaje" xfId="4" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -530,10 +566,16 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Andrea Zafra" id="{5DF18B94-23D7-594E-9BFE-B0E5E8D6F8BE}" userId="26cda608a9b19d33" providerId="Windows Live"/>
+</personList>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -571,7 +613,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -677,7 +719,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -819,23 +861,31 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="C14" dT="2025-05-07T03:15:26.18" personId="{5DF18B94-23D7-594E-9BFE-B0E5E8D6F8BE}" id="{767A6EB5-AA15-9841-8FFA-C6DE2D457FE8}">
+    <text>Is it constant?</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33051D97-709F-4BD1-B350-8CFE7D780BAB}">
   <dimension ref="A1:B45"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -843,179 +893,179 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B5" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B9" s="2">
         <v>2020</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B10" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B14" s="2">
         <v>2019</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B15" s="3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B18" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B19" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B20" s="3" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B20" s="3" t="s">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B21" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B21" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B23" s="6" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27">
-        <v>19.899999999999999</v>
+        <v>17.690000000000001</v>
       </c>
       <c r="B27" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="1"/>
       <c r="B28" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" s="1"/>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>21</v>
       </c>
@@ -1025,171 +1075,149 @@
     <hyperlink ref="B5" r:id="rId1" xr:uid="{4D98C279-73AD-4AB2-9323-9B591B8571DA}"/>
     <hyperlink ref="B20" r:id="rId2" xr:uid="{1EACF6CF-75C5-4797-95A4-1413D2CCE2C3}"/>
     <hyperlink ref="B15" r:id="rId3" xr:uid="{029A1935-883B-4EE7-8F77-324D50592C88}"/>
+    <hyperlink ref="B10" r:id="rId4" xr:uid="{07A6E36D-66A1-2E44-BCEF-47A115E19C15}"/>
+    <hyperlink ref="B28" r:id="rId5" xr:uid="{0214E371-7494-BE4C-BD6E-C86265AA6F57}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId4"/>
+  <pageSetup orientation="portrait" r:id="rId6"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C67F47B2-2197-46D3-B563-3A87E9D3C5BA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C67F47B2-2197-46D3-B563-3A87E9D3C5BA}">
   <dimension ref="A1:H31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="31.7109375" customWidth="1"/>
-    <col min="2" max="2" width="40.5703125" customWidth="1"/>
-    <col min="3" max="3" width="27.85546875" customWidth="1"/>
-    <col min="4" max="4" width="23.7109375" customWidth="1"/>
-    <col min="5" max="5" width="49.7109375" customWidth="1"/>
-    <col min="6" max="6" width="30.140625" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="31.6640625" customWidth="1"/>
+    <col min="2" max="2" width="40.5" customWidth="1"/>
+    <col min="3" max="3" width="27.83203125" customWidth="1"/>
+    <col min="4" max="4" width="23.6640625" customWidth="1"/>
+    <col min="5" max="5" width="49.6640625" customWidth="1"/>
+    <col min="6" max="6" width="30.1640625" hidden="1" customWidth="1"/>
     <col min="7" max="7" width="33" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="24.140625" customWidth="1"/>
-    <col min="9" max="9" width="29.5703125" customWidth="1"/>
+    <col min="8" max="8" width="24.1640625" customWidth="1"/>
+    <col min="9" max="9" width="29.5" customWidth="1"/>
     <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="25"/>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="29"/>
-      <c r="B2" s="30" t="s">
+    <row r="1" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="21"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="24"/>
+      <c r="B2" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="31"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="26"/>
       <c r="G2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="32"/>
-      <c r="B3" s="8" t="s">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" s="27"/>
+      <c r="B3" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="28"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="32"/>
-      <c r="B4" s="8" t="s">
+      <c r="E3" s="23"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" s="27"/>
+      <c r="B4" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="28"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="32"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="28"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="32"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="28"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="32"/>
-      <c r="B7" s="8" t="s">
+      <c r="E4" s="23"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" s="27"/>
+      <c r="E5" s="23"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" s="27"/>
+      <c r="C6" t="s">
+        <v>81</v>
+      </c>
+      <c r="E6" s="23"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" s="27"/>
+      <c r="B7" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="28"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="32"/>
-      <c r="B8" s="8" t="s">
+      <c r="E7" s="23"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" s="27"/>
+      <c r="B8" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="28"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="32"/>
-      <c r="B9" s="8" t="s">
+      <c r="E8" s="23"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" s="27"/>
+      <c r="B9" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="28"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="32"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="28"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="32"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="28"/>
+      <c r="E9" s="23"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" s="27"/>
+      <c r="E10" s="23"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" s="27"/>
+      <c r="D11" t="s">
+        <v>77</v>
+      </c>
+      <c r="E11" s="23" t="s">
+        <v>78</v>
+      </c>
       <c r="G11" s="3" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="32"/>
-      <c r="B12" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="C12" s="8">
-        <v>9946</v>
-      </c>
-      <c r="D12" s="8" t="s">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" s="27"/>
+      <c r="B12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C12">
+        <v>13790.02</v>
+      </c>
+      <c r="D12" t="s">
         <v>35</v>
       </c>
-      <c r="E12" s="28"/>
+      <c r="E12" s="23"/>
       <c r="G12" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="32"/>
-      <c r="B13" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="C13" s="8">
-        <v>65297.5</v>
-      </c>
-      <c r="D13" s="8" t="s">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13" s="27"/>
+      <c r="B13" t="s">
+        <v>74</v>
+      </c>
+      <c r="C13">
+        <v>82769.41</v>
+      </c>
+      <c r="D13" t="s">
         <v>35</v>
       </c>
-      <c r="E13" s="28"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="32"/>
-      <c r="B14" s="8" t="s">
+      <c r="E13" s="23"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14" s="27"/>
+      <c r="B14" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="9">
+      <c r="C14" s="33">
         <v>0.12</v>
       </c>
-      <c r="D14" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="E14" s="28"/>
+      <c r="D14" t="s">
+        <v>62</v>
+      </c>
+      <c r="E14" s="23"/>
       <c r="F14" t="s">
         <v>44</v>
       </c>
@@ -1197,281 +1225,267 @@
         <v>645.45000000000005</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="32"/>
-      <c r="B15" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="C15" s="26">
-        <f>(24443*0.533)/About!A27</f>
-        <v>654.67934673366847</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="E15" s="33"/>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15" s="27"/>
+      <c r="B15" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15" s="22">
+        <f>(31855566*0.5277)/(About!A27*1000)</f>
+        <v>950.26467937817972</v>
+      </c>
+      <c r="D15" t="s">
+        <v>79</v>
+      </c>
+      <c r="E15" s="34" t="s">
+        <v>82</v>
+      </c>
       <c r="F15" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="G15" s="20">
+      <c r="G15" s="17">
         <f>SUM(G16:G17)</f>
-        <v>645450000393.67261</v>
+        <v>645450000595.91772</v>
       </c>
       <c r="H15" s="3"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="32"/>
-      <c r="B16" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="C16" s="26">
-        <f>393672584853.823/10^9</f>
-        <v>393.67258485382303</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E16" s="34"/>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A16" s="27"/>
+      <c r="B16" t="s">
+        <v>67</v>
+      </c>
+      <c r="C16" s="22">
+        <f>595917670218/10^9</f>
+        <v>595.91767021800001</v>
+      </c>
+      <c r="D16" t="s">
+        <v>76</v>
+      </c>
+      <c r="E16" s="34" t="s">
+        <v>75</v>
+      </c>
       <c r="F16" t="s">
         <v>43</v>
       </c>
-      <c r="G16" s="20">
+      <c r="G16" s="17">
         <f>C16</f>
-        <v>393.67258485382303</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="32"/>
-      <c r="B17" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="C17" s="27">
+        <v>595.91767021800001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="27"/>
+      <c r="B17" t="s">
+        <v>68</v>
+      </c>
+      <c r="C17" s="7">
         <f>C15-C16</f>
-        <v>261.00676187984544</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="E17" s="35"/>
-      <c r="F17" s="21" t="s">
+        <v>354.34700916017971</v>
+      </c>
+      <c r="D17" t="s">
+        <v>63</v>
+      </c>
+      <c r="E17" s="28"/>
+      <c r="F17" t="s">
         <v>31</v>
       </c>
-      <c r="G17" s="19">
+      <c r="G17" s="16">
         <f>G14*10^9</f>
         <v>645450000000</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="32"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="28"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="32"/>
-      <c r="B19" s="8" t="s">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" s="27"/>
+      <c r="E18" s="23"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" s="27"/>
+      <c r="B19" t="s">
         <v>32</v>
       </c>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="28"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="32"/>
-      <c r="B20" s="8" t="s">
+      <c r="E19" s="23"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20" s="27"/>
+      <c r="B20" t="s">
         <v>33</v>
       </c>
-      <c r="C20" s="11">
+      <c r="C20" s="8">
         <f>C12/C13</f>
-        <v>0.15231823576706613</v>
-      </c>
-      <c r="D20" s="8" t="s">
+        <v>0.16660768755026767</v>
+      </c>
+      <c r="D20" t="s">
+        <v>63</v>
+      </c>
+      <c r="E20" s="23"/>
+      <c r="F20" t="s">
+        <v>33</v>
+      </c>
+      <c r="G20" s="8">
+        <f>C12/C13</f>
+        <v>0.16660768755026767</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21" s="27"/>
+      <c r="B21" t="s">
+        <v>36</v>
+      </c>
+      <c r="C21" s="8">
+        <f>1-C22</f>
+        <v>0.98000707749396787</v>
+      </c>
+      <c r="D21" t="s">
         <v>64</v>
       </c>
-      <c r="E20" s="28"/>
-      <c r="F20" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="G20" s="11">
-        <f>C12/C13</f>
-        <v>0.15231823576706613</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="32"/>
-      <c r="B21" s="8" t="s">
+      <c r="E21" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="F21" t="s">
         <v>36</v>
       </c>
-      <c r="C21" s="11">
-        <f>1-C22</f>
-        <v>0.98172181170795203</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="E21" s="28" t="s">
-        <v>74</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="32"/>
-      <c r="B22" s="8" t="s">
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A22" s="27"/>
+      <c r="B22" t="s">
         <v>34</v>
       </c>
-      <c r="C22" s="11">
+      <c r="C22" s="8">
         <f>C20*C14</f>
-        <v>1.8278188292047935E-2</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="E22" s="28" t="s">
-        <v>74</v>
-      </c>
-      <c r="F22" s="8" t="s">
+        <v>1.9992922506032119E-2</v>
+      </c>
+      <c r="D22" t="s">
+        <v>64</v>
+      </c>
+      <c r="E22" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="F22" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="32"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="28"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="32"/>
-      <c r="B24" s="8" t="s">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A23" s="27"/>
+      <c r="E23" s="23"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A24" s="27"/>
+      <c r="B24" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="28"/>
-      <c r="F24" s="8" t="s">
+      <c r="E24" s="23"/>
+      <c r="F24" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="32"/>
-      <c r="B25" s="8" t="s">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A25" s="27"/>
+      <c r="B25" t="s">
         <v>4</v>
       </c>
-      <c r="C25" s="10">
+      <c r="C25" s="7">
         <f>C17*C21</f>
-        <v>256.23603114070789</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="E25" s="28"/>
-      <c r="F25" s="8" t="s">
+        <v>347.26257686579601</v>
+      </c>
+      <c r="D25" t="s">
+        <v>63</v>
+      </c>
+      <c r="E25" s="23"/>
+      <c r="F25" t="s">
         <v>4</v>
       </c>
-      <c r="G25" s="20">
+      <c r="G25" s="17">
         <f>G17*C21</f>
-        <v>633652343366.89758</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="32"/>
-      <c r="B26" s="8" t="s">
+        <v>632545568168.48157</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A26" s="27"/>
+      <c r="B26" t="s">
         <v>3</v>
       </c>
-      <c r="C26" s="10">
+      <c r="C26" s="7">
         <f>C17*C22</f>
-        <v>4.7707307391375346</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="E26" s="28"/>
-      <c r="F26" s="8" t="s">
+        <v>7.0844322943837259</v>
+      </c>
+      <c r="D26" t="s">
+        <v>63</v>
+      </c>
+      <c r="E26" s="23"/>
+      <c r="F26" t="s">
         <v>3</v>
       </c>
-      <c r="G26" s="20">
+      <c r="G26" s="17">
         <f>G17*C22</f>
-        <v>11797656633.102341</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="32"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="8"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="28"/>
-    </row>
-    <row r="28" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="32"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="28"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="40" t="s">
+        <v>12904431831.518431</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A27" s="27"/>
+      <c r="E27" s="23"/>
+    </row>
+    <row r="28" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="27"/>
+      <c r="E28" s="23"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="B29" s="15" t="s">
+      <c r="B29" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C29" s="16">
+      <c r="C29" s="13">
         <f>C25/C15</f>
-        <v>0.39139165214104094</v>
-      </c>
-      <c r="D29" s="8"/>
-      <c r="E29" s="28" t="s">
+        <v>0.36543774003368473</v>
+      </c>
+      <c r="E29" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="F29" s="15" t="s">
+      <c r="F29" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="G29" s="22">
+      <c r="G29" s="18">
         <f>G25/G15</f>
-        <v>0.98172181110918055</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="41"/>
-      <c r="B30" s="12" t="s">
+        <v>0.98000707658916719</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="32"/>
+      <c r="B30" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="C30" s="17">
+      <c r="C30" s="14">
         <f>C26/C15</f>
-        <v>7.2871257707146303E-3</v>
-      </c>
-      <c r="D30" s="8"/>
-      <c r="E30" s="28"/>
-      <c r="F30" s="12" t="s">
+        <v>7.4552200540795987E-3</v>
+      </c>
+      <c r="E30" s="23"/>
+      <c r="F30" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="G30" s="23">
+      <c r="G30" s="19">
         <f>G26/G15</f>
-        <v>1.8278188280899711E-2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="14" t="s">
+        <v>1.9992922487573467E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="B31" s="13" t="s">
+      <c r="B31" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C31" s="18">
+      <c r="C31" s="15">
         <f>C16/C15</f>
-        <v>0.60132122208824446</v>
-      </c>
-      <c r="D31" s="36"/>
-      <c r="E31" s="37"/>
-      <c r="F31" s="13" t="s">
+        <v>0.62710703991223571</v>
+      </c>
+      <c r="D31" s="29"/>
+      <c r="E31" s="30"/>
+      <c r="F31" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="G31" s="24">
+      <c r="G31" s="20">
         <f>G16/G15</f>
-        <v>6.099195671449599E-10</v>
+        <v>9.2325922947991862E-10</v>
       </c>
     </row>
   </sheetData>
@@ -1482,6 +1496,7 @@
     <hyperlink ref="G11" r:id="rId1" location=":~:text=In%202019%2C%20the%20national%20debt,around%20645.45%20billion%20U.S.%20dollars." xr:uid="{B16E5236-2FFD-4922-87E4-3FD200B1C734}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -1490,14 +1505,14 @@
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="36.85546875" customWidth="1"/>
-    <col min="2" max="2" width="22.42578125" customWidth="1"/>
+    <col min="1" max="1" width="36.83203125" customWidth="1"/>
+    <col min="2" max="2" width="22.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
         <v>13</v>
       </c>
@@ -1505,88 +1520,262 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="38">
+      <c r="B2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="39">
+      <c r="B3" s="4">
         <f>Calcs!C29</f>
-        <v>0.39139165214104094</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.36543774003368473</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="39">
+      <c r="B4" s="4">
         <f>Calcs!C30</f>
-        <v>7.2871257707146303E-3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7.4552200540795987E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="39">
+      <c r="B5" s="4">
         <f>Calcs!C31</f>
-        <v>0.60132122208824446</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.62710703991223571</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="38">
+      <c r="B6">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="38">
+      <c r="B7">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="38">
+      <c r="B8">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="38">
+      <c r="B9">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="38">
+      <c r="B10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B11" s="38"/>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B12" s="38"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009A9DAB439B36DB4795F39C4E722C7BC4" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="44674c89fa9bc5e97a878a6680c46188">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="79748b23-d81a-423e-9112-21109dc864e6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="447839a363ea5a12024b5bf1ab53ed90" ns2:_="">
+    <xsd:import namespace="79748b23-d81a-423e-9112-21109dc864e6"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="79748b23-d81a-423e-9112-21109dc864e6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A334903-C6FD-4E4F-A8AF-8FBCD7D09E6D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8EF33493-2565-42F1-B2AD-4C68C61999A4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4015F40-4B5F-4FF3-A678-F6847C8D21AC}"/>
 </file>